--- a/DOM/AFOLU/A1_Inputs/A-I_Classifier_Modes_Transport.xlsx
+++ b/DOM/AFOLU/A1_Inputs/A-I_Classifier_Modes_Transport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://clgcr.sharepoint.com/sites/ClimateLeadGroup-Decarb_RD/Documentos compartidos/Decarb_RD/WBG/4_Model/RD_Model_v7_Lucía/A1_Inputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://clgcr.sharepoint.com/sites/ClimateLeadGroup-Decarb_RD/Documentos compartidos/Decarb_RD/WBG/04_Model/RD_model_int_NZ6/A1_Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="106_{8D290350-7B29-4947-B92D-E4D9559AD5B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89A40EBA-C802-448F-873E-6D6EA17FF947}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="106_{8D290350-7B29-4947-B92D-E4D9559AD5B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06A45CB5-BE93-45B8-A56A-22F692F3B609}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="864" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34635" yWindow="3735" windowWidth="21600" windowHeight="11235" tabRatio="864" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mode_Broad" sheetId="2" r:id="rId1"/>
@@ -49,9 +49,9 @@
   <commentList>
     <comment ref="B2" authorId="0" shapeId="0" xr:uid="{8E173E61-7A36-4940-93D3-48588AAA0DB4}">
       <text>
-        <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Correspondería a taxis</t>
       </text>
     </comment>
@@ -366,7 +366,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -411,12 +411,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1163,7 +1157,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1498,9 +1492,9 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:F13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
@@ -1684,7 +1678,7 @@
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -1976,7 +1970,7 @@
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="7" width="12.109375" customWidth="1"/>
   </cols>
@@ -2121,7 +2115,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1A324D-A0AB-4ECB-9BF7-BF12A7A5F3A8}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5546875" bestFit="1" customWidth="1"/>
@@ -2234,7 +2228,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C470471-C426-469F-9ED6-2FEDE78EC2A1}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5546875" bestFit="1" customWidth="1"/>
@@ -2376,7 +2370,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3026DB6-0F59-4D5E-A6F2-AAED52E94AFB}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.109375" bestFit="1" customWidth="1"/>
@@ -2574,7 +2568,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5A31B68-9A1C-4ACF-9DFA-B94C351D7F54}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.109375" customWidth="1"/>
@@ -2653,19 +2647,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="160a8fee-1065-46af-a09f-4bc299cd7729" xsi:nil="true"/>
+    <TaxCatchAll xmlns="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CCDA0DC61E44874FB77B81A0A8C300E4" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="71904d85c9bd1373b9e56b88e8365113">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9c2c21c4-f980-47d5-be5b-1bb924ee96a2" xmlns:ns3="1b6bb729-2ef5-410d-b4d4-7ced22c361d1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7f50eb003d4f8624802c7eda0096d7ec" ns2:_="" ns3:_="">
-    <xsd:import namespace="9c2c21c4-f980-47d5-be5b-1bb924ee96a2"/>
-    <xsd:import namespace="1b6bb729-2ef5-410d-b4d4-7ced22c361d1"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000D404091916B8749A73FDE0336A1D2B1" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="97d759966af21adcadc0b99feda85e1a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="160a8fee-1065-46af-a09f-4bc299cd7729" xmlns:ns3="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c4a9b885529ac7a0313cb8fba8dc54f0" ns2:_="" ns3:_="">
+    <xsd:import namespace="160a8fee-1065-46af-a09f-4bc299cd7729"/>
+    <xsd:import namespace="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -2674,18 +2668,13 @@
               <xsd:all>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2693,7 +2682,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9c2c21c4-f980-47d5-be5b-1bb924ee96a2" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="160a8fee-1065-46af-a09f-4bc299cd7729" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -2706,91 +2695,52 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:displayName="Etiquetas de imagen_0" ma:hidden="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="13" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="71f7bd95-1200-4052-9a4e-dfdf006e181b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="21" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1b6bb729-2ef5-410d-b4d4-7ced22c361d1" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="14" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="TaxCatchAll" ma:index="12" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{358d400d-8031-419e-a2bc-623ab747dbff}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99">
       <xsd:complexType>
         <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
+          <xsd:extension base="dms:MultiChoiceLookup">
             <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
             </xsd:sequence>
           </xsd:extension>
         </xsd:complexContent>
       </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="15" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -2802,8 +2752,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -2893,28 +2843,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9c2c21c4-f980-47d5-be5b-1bb924ee96a2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11D5A8F3-5231-46A6-A9EE-D0E0BC5EF750}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68DA7AFD-D5E9-410F-836F-A3D9F3E96BF8}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8ABA9104-BC13-491B-AC54-17D816A8EDDE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -2929,4 +2866,16 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7ED4CA6F-8BEF-4DF9-8687-66C65433FCE3}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11D5A8F3-5231-46A6-A9EE-D0E0BC5EF750}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>